--- a/price_bank/test/fixtures_private/Desalters_bank_test_messy.xlsx
+++ b/price_bank/test/fixtures_private/Desalters_bank_test_messy.xlsx
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:AN15"/>
+  <dimension ref="A3:AO15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="3">
@@ -1133,6 +1133,11 @@
           <t>Record ID</t>
         </is>
       </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Site Altitude (m)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1302,9 @@
           <t>DES-0001</t>
         </is>
       </c>
+      <c r="AO7" t="n">
+        <v>705</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1469,9 @@
           <t>DES-0002</t>
         </is>
       </c>
+      <c r="AO8" t="n">
+        <v>706</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1630,6 +1641,9 @@
           <t>DES-0003</t>
         </is>
       </c>
+      <c r="AO9" t="n">
+        <v>707</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1799,6 +1813,9 @@
           <t>DES-0004</t>
         </is>
       </c>
+      <c r="AO10" t="n">
+        <v>708</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1962,6 +1979,9 @@
           <t>DES-0005</t>
         </is>
       </c>
+      <c r="AO11" t="n">
+        <v>709</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2125,6 +2145,9 @@
           <t>DES-0006</t>
         </is>
       </c>
+      <c r="AO12" t="n">
+        <v>710</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2273,6 +2296,9 @@
           <t>DES-0007</t>
         </is>
       </c>
+      <c r="AO13" t="n">
+        <v>711</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2427,6 +2453,9 @@
           <t>DES-0008</t>
         </is>
       </c>
+      <c r="AO14" t="n">
+        <v>712</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2585,6 +2614,9 @@
         <is>
           <t>DES-0009</t>
         </is>
+      </c>
+      <c r="AO15" t="n">
+        <v>713</v>
       </c>
     </row>
   </sheetData>
